--- a/02_DIA_inicio_2026_analisis_assets/rbd_9734_escuela-raul-saez-saez_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9734_escuela-raul-saez-saez_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{286506FC-A3C7-4E73-9C07-759527628140}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F94AB26E-A795-43C3-BC75-9E8428CCD425}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF34C537-8916-458A-B8FE-F2EF17FB6FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1ACC58D-9868-41DE-88BA-7A36092AE2B6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A3898F-FB10-491A-85A9-12C61EDFBFE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{341ADFC5-2BD8-4A40-AB4A-2109B1CF1B46}"/>
 </file>